--- a/content/sources/model_test_workbook.xlsx
+++ b/content/sources/model_test_workbook.xlsx
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C247"/>
+  <dimension ref="A1:C251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Q156</t>
+          <t>Q240</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>MTQ-002</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Q240</t>
+          <t>MTQ-031</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MTQ-002</t>
+          <t>MTQ-004</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MTQ-031</t>
+          <t>Q243</t>
         </is>
       </c>
     </row>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MTQ-004</t>
+          <t>Q149</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>mt2</t>
+          <t>mt1</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q095</t>
         </is>
       </c>
     </row>
@@ -1390,11 +1390,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q006</t>
         </is>
       </c>
     </row>
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q008</t>
         </is>
       </c>
     </row>
@@ -1420,11 +1420,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Q069</t>
+          <t>Q010</t>
         </is>
       </c>
     </row>
@@ -1435,11 +1435,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q069</t>
         </is>
       </c>
     </row>
@@ -1450,11 +1450,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Q078</t>
+          <t>Q013</t>
         </is>
       </c>
     </row>
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q078</t>
         </is>
       </c>
     </row>
@@ -1480,11 +1480,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q011</t>
         </is>
       </c>
     </row>
@@ -1495,11 +1495,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Q057</t>
+          <t>Q012</t>
         </is>
       </c>
     </row>
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Q076</t>
+          <t>Q057</t>
         </is>
       </c>
     </row>
@@ -1525,11 +1525,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Q048</t>
+          <t>Q076</t>
         </is>
       </c>
     </row>
@@ -1540,11 +1540,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q048</t>
         </is>
       </c>
     </row>
@@ -1555,11 +1555,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MTQ-016</t>
+          <t>Q015</t>
         </is>
       </c>
     </row>
@@ -1570,11 +1570,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MTQ-065</t>
+          <t>MTQ-016</t>
         </is>
       </c>
     </row>
@@ -1585,11 +1585,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MTQ-015</t>
+          <t>MTQ-065</t>
         </is>
       </c>
     </row>
@@ -1600,11 +1600,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MTQ-068</t>
+          <t>MTQ-015</t>
         </is>
       </c>
     </row>
@@ -1615,11 +1615,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Q100</t>
+          <t>MTQ-068</t>
         </is>
       </c>
     </row>
@@ -1630,11 +1630,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Q106</t>
+          <t>Q100</t>
         </is>
       </c>
     </row>
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q106</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1750,11 +1750,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Q103</t>
+          <t>Q143</t>
         </is>
       </c>
     </row>
@@ -1765,11 +1765,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Q143</t>
+          <t>MTQ-058</t>
         </is>
       </c>
     </row>
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MTQ-058</t>
+          <t>MTQ-013</t>
         </is>
       </c>
     </row>
@@ -1795,11 +1795,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MTQ-013</t>
+          <t>MTQ-077</t>
         </is>
       </c>
     </row>
@@ -1810,11 +1810,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MTQ-077</t>
+          <t>Q004</t>
         </is>
       </c>
     </row>
@@ -1825,11 +1825,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q152</t>
         </is>
       </c>
     </row>
@@ -1840,11 +1840,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Q096</t>
+          <t>Q158</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Q152</t>
+          <t>Q161</t>
         </is>
       </c>
     </row>
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Q158</t>
+          <t>Q163</t>
         </is>
       </c>
     </row>
@@ -1885,11 +1885,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Q161</t>
+          <t>Q172</t>
         </is>
       </c>
     </row>
@@ -1900,11 +1900,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Q163</t>
+          <t>MTQ-024</t>
         </is>
       </c>
     </row>
@@ -1915,11 +1915,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Q172</t>
+          <t>MTQ-048</t>
         </is>
       </c>
     </row>
@@ -1930,11 +1930,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MTQ-024</t>
+          <t>MTQ-020</t>
         </is>
       </c>
     </row>
@@ -1945,11 +1945,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MTQ-048</t>
+          <t>Q242</t>
         </is>
       </c>
     </row>
@@ -1960,11 +1960,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MTQ-020</t>
+          <t>Q252</t>
         </is>
       </c>
     </row>
@@ -1975,11 +1975,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Q242</t>
+          <t>Q173</t>
         </is>
       </c>
     </row>
@@ -1990,11 +1990,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Q252</t>
+          <t>Q286</t>
         </is>
       </c>
     </row>
@@ -2005,11 +2005,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Q173</t>
+          <t>MTQ-053</t>
         </is>
       </c>
     </row>
@@ -2020,11 +2020,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Q286</t>
+          <t>Q244</t>
         </is>
       </c>
     </row>
@@ -2035,11 +2035,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MTQ-053</t>
+          <t>MTQ-073</t>
         </is>
       </c>
     </row>
@@ -2050,11 +2050,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Q244</t>
+          <t>MTQ-032</t>
         </is>
       </c>
     </row>
@@ -2065,11 +2065,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MTQ-073</t>
+          <t>MTQ-075</t>
         </is>
       </c>
     </row>
@@ -2080,11 +2080,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MTQ-032</t>
+          <t>Q107</t>
         </is>
       </c>
     </row>
@@ -2095,41 +2095,41 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MTQ-075</t>
+          <t>Q108</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mt3</t>
+          <t>mt2</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q245</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mt3</t>
+          <t>mt2</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q112</t>
         </is>
       </c>
     </row>
@@ -2140,11 +2140,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Q079</t>
+          <t>Q014</t>
         </is>
       </c>
     </row>
@@ -2155,11 +2155,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q010</t>
         </is>
       </c>
     </row>
@@ -2170,11 +2170,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q079</t>
         </is>
       </c>
     </row>
@@ -2185,11 +2185,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q019</t>
         </is>
       </c>
     </row>
@@ -2200,11 +2200,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Q044</t>
+          <t>Q016</t>
         </is>
       </c>
     </row>
@@ -2215,11 +2215,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q011</t>
         </is>
       </c>
     </row>
@@ -2230,11 +2230,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q044</t>
         </is>
       </c>
     </row>
@@ -2245,11 +2245,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Q086</t>
+          <t>Q020</t>
         </is>
       </c>
     </row>
@@ -2260,11 +2260,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q018</t>
         </is>
       </c>
     </row>
@@ -2275,11 +2275,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q086</t>
         </is>
       </c>
     </row>
@@ -2290,11 +2290,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MTQ-012</t>
+          <t>Q021</t>
         </is>
       </c>
     </row>
@@ -2305,11 +2305,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MTQ-038</t>
+          <t>Q022</t>
         </is>
       </c>
     </row>
@@ -2320,11 +2320,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MTQ-006</t>
+          <t>MTQ-012</t>
         </is>
       </c>
     </row>
@@ -2335,11 +2335,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Q111</t>
+          <t>MTQ-038</t>
         </is>
       </c>
     </row>
@@ -2350,11 +2350,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Q109</t>
+          <t>MTQ-006</t>
         </is>
       </c>
     </row>
@@ -2365,11 +2365,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Q098</t>
+          <t>Q111</t>
         </is>
       </c>
     </row>
@@ -2380,11 +2380,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Q114</t>
+          <t>Q109</t>
         </is>
       </c>
     </row>
@@ -2395,11 +2395,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MTQ-078</t>
+          <t>Q098</t>
         </is>
       </c>
     </row>
@@ -2410,11 +2410,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MTQ-055</t>
+          <t>Q114</t>
         </is>
       </c>
     </row>
@@ -2425,11 +2425,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MTQ-056</t>
+          <t>MTQ-078</t>
         </is>
       </c>
     </row>
@@ -2440,11 +2440,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Q111</t>
+          <t>MTQ-055</t>
         </is>
       </c>
     </row>
@@ -2455,11 +2455,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Q110</t>
+          <t>MTQ-056</t>
         </is>
       </c>
     </row>
@@ -2470,11 +2470,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Q102</t>
+          <t>Q110</t>
         </is>
       </c>
     </row>
@@ -2485,11 +2485,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Q121</t>
+          <t>Q102</t>
         </is>
       </c>
     </row>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MTQ-076</t>
+          <t>Q121</t>
         </is>
       </c>
     </row>
@@ -2515,11 +2515,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MTQ-009</t>
+          <t>MTQ-076</t>
         </is>
       </c>
     </row>
@@ -2530,11 +2530,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MTQ-061</t>
+          <t>MTQ-009</t>
         </is>
       </c>
     </row>
@@ -2545,11 +2545,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MTQ-028</t>
+          <t>MTQ-061</t>
         </is>
       </c>
     </row>
@@ -2560,11 +2560,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MTQ-072</t>
+          <t>MTQ-028</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Q142</t>
+          <t>MTQ-072</t>
         </is>
       </c>
     </row>
@@ -2590,11 +2590,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Q222</t>
+          <t>Q142</t>
         </is>
       </c>
     </row>
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Q102</t>
+          <t>Q222</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -2856,30 +2856,30 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>mt4</t>
+          <t>mt3</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q115</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>mt4</t>
+          <t>mt3</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Q286</t>
+          <t>Q247</t>
         </is>
       </c>
     </row>
@@ -2890,11 +2890,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Q046</t>
+          <t>Q023</t>
         </is>
       </c>
     </row>
@@ -2905,11 +2905,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q286</t>
         </is>
       </c>
     </row>
@@ -2920,11 +2920,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q046</t>
         </is>
       </c>
     </row>
@@ -2935,11 +2935,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MTQ-051</t>
+          <t>Q024</t>
         </is>
       </c>
     </row>
@@ -2950,11 +2950,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q030</t>
         </is>
       </c>
     </row>
@@ -2965,11 +2965,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>MTQ-051</t>
         </is>
       </c>
     </row>
@@ -2980,11 +2980,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Q076</t>
+          <t>Q025</t>
         </is>
       </c>
     </row>
@@ -2995,11 +2995,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MTQ-005</t>
+          <t>Q032</t>
         </is>
       </c>
     </row>
@@ -3010,11 +3010,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q076</t>
         </is>
       </c>
     </row>
@@ -3025,11 +3025,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>MTQ-005</t>
         </is>
       </c>
     </row>
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MTQ-034</t>
+          <t>Q026</t>
         </is>
       </c>
     </row>
@@ -3055,11 +3055,11 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MTQ-067</t>
+          <t>Q037</t>
         </is>
       </c>
     </row>
@@ -3070,11 +3070,11 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MTQ-017</t>
+          <t>MTQ-034</t>
         </is>
       </c>
     </row>
@@ -3085,11 +3085,11 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Q135</t>
+          <t>MTQ-067</t>
         </is>
       </c>
     </row>
@@ -3100,11 +3100,11 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MTQ-054</t>
+          <t>MTQ-017</t>
         </is>
       </c>
     </row>
@@ -3115,11 +3115,11 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Q122</t>
+          <t>Q135</t>
         </is>
       </c>
     </row>
@@ -3130,11 +3130,11 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Q111</t>
+          <t>MTQ-054</t>
         </is>
       </c>
     </row>
@@ -3145,11 +3145,11 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Q104</t>
+          <t>Q122</t>
         </is>
       </c>
     </row>
@@ -3160,11 +3160,11 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Q100</t>
+          <t>Q111</t>
         </is>
       </c>
     </row>
@@ -3175,11 +3175,11 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Q142</t>
+          <t>Q104</t>
         </is>
       </c>
     </row>
@@ -3190,11 +3190,11 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Q096</t>
+          <t>Q100</t>
         </is>
       </c>
     </row>
@@ -3205,11 +3205,11 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Q122</t>
+          <t>Q142</t>
         </is>
       </c>
     </row>
@@ -3220,11 +3220,11 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Q148</t>
+          <t>Q096</t>
         </is>
       </c>
     </row>
@@ -3235,11 +3235,11 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Q060</t>
+          <t>Q148</t>
         </is>
       </c>
     </row>
@@ -3250,11 +3250,11 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Q099</t>
+          <t>Q060</t>
         </is>
       </c>
     </row>
@@ -3265,11 +3265,11 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MTQ-062</t>
+          <t>Q099</t>
         </is>
       </c>
     </row>
@@ -3280,11 +3280,11 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MTQ-036</t>
+          <t>MTQ-062</t>
         </is>
       </c>
     </row>
@@ -3295,11 +3295,11 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MTQ-040</t>
+          <t>MTQ-036</t>
         </is>
       </c>
     </row>
@@ -3310,11 +3310,11 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>MTQ-064</t>
+          <t>MTQ-040</t>
         </is>
       </c>
     </row>
@@ -3325,11 +3325,11 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Q150</t>
+          <t>MTQ-064</t>
         </is>
       </c>
     </row>
@@ -3340,11 +3340,11 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>MTQ-057</t>
+          <t>Q150</t>
         </is>
       </c>
     </row>
@@ -3355,11 +3355,11 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Q175</t>
+          <t>MTQ-057</t>
         </is>
       </c>
     </row>
@@ -3370,11 +3370,11 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Q182</t>
+          <t>Q175</t>
         </is>
       </c>
     </row>
@@ -3385,11 +3385,11 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Q189</t>
+          <t>Q182</t>
         </is>
       </c>
     </row>
@@ -3400,11 +3400,11 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MTQ-008</t>
+          <t>Q189</t>
         </is>
       </c>
     </row>
@@ -3415,11 +3415,11 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>MTQ-018</t>
+          <t>MTQ-008</t>
         </is>
       </c>
     </row>
@@ -3430,11 +3430,11 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MTQ-037</t>
+          <t>MTQ-018</t>
         </is>
       </c>
     </row>
@@ -3445,11 +3445,11 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Q246</t>
+          <t>MTQ-037</t>
         </is>
       </c>
     </row>
@@ -3460,11 +3460,11 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Q244</t>
+          <t>Q246</t>
         </is>
       </c>
     </row>
@@ -3475,11 +3475,11 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Q258</t>
+          <t>Q244</t>
         </is>
       </c>
     </row>
@@ -3490,11 +3490,11 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Q205</t>
+          <t>Q258</t>
         </is>
       </c>
     </row>
@@ -3505,11 +3505,11 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Q246</t>
+          <t>Q205</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -3591,45 +3591,45 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mt5</t>
+          <t>mt4</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q117</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mt5</t>
+          <t>mt4</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q155</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mt5</t>
+          <t>mt4</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q029</t>
         </is>
       </c>
     </row>
@@ -3640,11 +3640,11 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q002</t>
         </is>
       </c>
     </row>
@@ -3655,11 +3655,11 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Q043</t>
+          <t>Q038</t>
         </is>
       </c>
     </row>
@@ -3670,11 +3670,11 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Q086</t>
+          <t>Q003</t>
         </is>
       </c>
     </row>
@@ -3685,11 +3685,11 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MTQ-001</t>
+          <t>Q016</t>
         </is>
       </c>
     </row>
@@ -3700,11 +3700,11 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Q045</t>
+          <t>Q043</t>
         </is>
       </c>
     </row>
@@ -3715,11 +3715,11 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q086</t>
         </is>
       </c>
     </row>
@@ -3730,11 +3730,11 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Q046</t>
+          <t>MTQ-001</t>
         </is>
       </c>
     </row>
@@ -3745,11 +3745,11 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q045</t>
         </is>
       </c>
     </row>
@@ -3760,11 +3760,11 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>MTQ-052</t>
+          <t>Q027</t>
         </is>
       </c>
     </row>
@@ -3775,11 +3775,11 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>MTQ-049</t>
+          <t>Q046</t>
         </is>
       </c>
     </row>
@@ -3790,11 +3790,11 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>MTQ-033</t>
+          <t>Q028</t>
         </is>
       </c>
     </row>
@@ -3805,11 +3805,11 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>MTQ-022</t>
+          <t>MTQ-052</t>
         </is>
       </c>
     </row>
@@ -3820,11 +3820,11 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Q109</t>
+          <t>MTQ-049</t>
         </is>
       </c>
     </row>
@@ -3835,11 +3835,11 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Q113</t>
+          <t>MTQ-033</t>
         </is>
       </c>
     </row>
@@ -3850,11 +3850,11 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>MTQ-070</t>
+          <t>MTQ-022</t>
         </is>
       </c>
     </row>
@@ -3865,11 +3865,11 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Q116</t>
+          <t>Q109</t>
         </is>
       </c>
     </row>
@@ -3880,11 +3880,11 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Q096</t>
+          <t>Q113</t>
         </is>
       </c>
     </row>
@@ -3895,11 +3895,11 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>MTQ-030</t>
+          <t>MTQ-070</t>
         </is>
       </c>
     </row>
@@ -3910,11 +3910,11 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Q133</t>
+          <t>Q116</t>
         </is>
       </c>
     </row>
@@ -3925,11 +3925,11 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Q104</t>
+          <t>Q096</t>
         </is>
       </c>
     </row>
@@ -3940,11 +3940,11 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Q141</t>
+          <t>MTQ-030</t>
         </is>
       </c>
     </row>
@@ -3955,11 +3955,11 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Q092</t>
+          <t>Q133</t>
         </is>
       </c>
     </row>
@@ -3970,11 +3970,11 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Q093</t>
+          <t>Q104</t>
         </is>
       </c>
     </row>
@@ -3985,11 +3985,11 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Q101</t>
+          <t>Q141</t>
         </is>
       </c>
     </row>
@@ -4000,11 +4000,11 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>MTQ-046</t>
+          <t>Q092</t>
         </is>
       </c>
     </row>
@@ -4015,11 +4015,11 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>MTQ-014</t>
+          <t>Q093</t>
         </is>
       </c>
     </row>
@@ -4030,11 +4030,11 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>MTQ-039</t>
+          <t>Q101</t>
         </is>
       </c>
     </row>
@@ -4045,11 +4045,11 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Q151</t>
+          <t>MTQ-046</t>
         </is>
       </c>
     </row>
@@ -4060,11 +4060,11 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Q169</t>
+          <t>MTQ-014</t>
         </is>
       </c>
     </row>
@@ -4075,11 +4075,11 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Q165</t>
+          <t>MTQ-039</t>
         </is>
       </c>
     </row>
@@ -4090,11 +4090,11 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>MTQ-079</t>
+          <t>Q151</t>
         </is>
       </c>
     </row>
@@ -4105,11 +4105,11 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Q210</t>
+          <t>Q169</t>
         </is>
       </c>
     </row>
@@ -4120,11 +4120,11 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Q223</t>
+          <t>Q165</t>
         </is>
       </c>
     </row>
@@ -4135,11 +4135,11 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>MTQ-019</t>
+          <t>MTQ-079</t>
         </is>
       </c>
     </row>
@@ -4150,11 +4150,11 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>MTQ-023</t>
+          <t>Q210</t>
         </is>
       </c>
     </row>
@@ -4165,11 +4165,11 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>MTQ-011</t>
+          <t>Q223</t>
         </is>
       </c>
     </row>
@@ -4180,11 +4180,11 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Q253</t>
+          <t>MTQ-019</t>
         </is>
       </c>
     </row>
@@ -4195,11 +4195,11 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>MTQ-080</t>
+          <t>MTQ-023</t>
         </is>
       </c>
     </row>
@@ -4210,11 +4210,11 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Q260</t>
+          <t>MTQ-011</t>
         </is>
       </c>
     </row>
@@ -4225,11 +4225,11 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Q286</t>
+          <t>Q253</t>
         </is>
       </c>
     </row>
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Q257</t>
+          <t>MTQ-080</t>
         </is>
       </c>
     </row>
@@ -4255,11 +4255,11 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Q274</t>
+          <t>Q260</t>
         </is>
       </c>
     </row>
@@ -4270,11 +4270,11 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Q262</t>
+          <t>Q286</t>
         </is>
       </c>
     </row>
@@ -4285,11 +4285,11 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>MTQ-042</t>
+          <t>Q257</t>
         </is>
       </c>
     </row>
@@ -4300,11 +4300,11 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>MTQ-043</t>
+          <t>Q274</t>
         </is>
       </c>
     </row>
@@ -4315,11 +4315,71 @@
         </is>
       </c>
       <c r="B247" t="n">
+        <v>46</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Q262</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>mt5</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>47</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>MTQ-042</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>mt5</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>48</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>MTQ-043</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>mt5</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
         <v>49</v>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>MTQ-074</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>mt5</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>50</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Q162</t>
         </is>
       </c>
     </row>

--- a/content/sources/model_test_workbook.xlsx
+++ b/content/sources/model_test_workbook.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Q092</t>
+          <t>Q093</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Q093</t>
+          <t>Q101</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Q101</t>
+          <t>Q127</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Q127</t>
+          <t>Q094</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Q094</t>
+          <t>Q099</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Q099</t>
+          <t>Q106</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Q106</t>
+          <t>Q032</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q124</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Q124</t>
+          <t>Q097</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Q097</t>
+          <t>Q105</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Q105</t>
+          <t>Q132</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Q132</t>
+          <t>MTQ-063</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MTQ-063</t>
+          <t>MTQ-041</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MTQ-041</t>
+          <t>MTQ-066</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MTQ-066</t>
+          <t>Q154</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Q154</t>
+          <t>Q153</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Q153</t>
+          <t>Q157</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Q157</t>
+          <t>Q156</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Q156</t>
+          <t>Q160</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Q160</t>
+          <t>Q159</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Q159</t>
+          <t>MTQ-010</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MTQ-010</t>
+          <t>MTQ-021</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MTQ-021</t>
+          <t>MTQ-050</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MTQ-050</t>
+          <t>Q250</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Q250</t>
+          <t>Q241</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Q241</t>
+          <t>Q249</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Q249</t>
+          <t>Q277</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Q277</t>
+          <t>Q240</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Q240</t>
+          <t>MTQ-002</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MTQ-002</t>
+          <t>MTQ-031</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MTQ-031</t>
+          <t>MTQ-004</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MTQ-004</t>
+          <t>Q243</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Q243</t>
+          <t>Q149</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Q149</t>
+          <t>Q095</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Q095</t>
+          <t>Q251</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q069</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Q069</t>
+          <t>Q013</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q078</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Q078</t>
+          <t>Q011</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q012</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q057</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Q057</t>
+          <t>Q076</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Q076</t>
+          <t>Q048</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Q048</t>
+          <t>Q015</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>MTQ-016</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MTQ-016</t>
+          <t>MTQ-065</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MTQ-065</t>
+          <t>MTQ-015</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MTQ-015</t>
+          <t>MTQ-068</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MTQ-068</t>
+          <t>Q100</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Q100</t>
+          <t>Q106</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Q106</t>
+          <t>Q123</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Q123</t>
+          <t>Q110</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Q110</t>
+          <t>MTQ-069</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MTQ-069</t>
+          <t>Q103</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Q096</t>
+          <t>Q133</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Q103</t>
+          <t>Q143</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Q133</t>
+          <t>MTQ-058</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Q143</t>
+          <t>MTQ-013</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MTQ-058</t>
+          <t>MTQ-077</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MTQ-013</t>
+          <t>Q152</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MTQ-077</t>
+          <t>Q158</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q161</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Q152</t>
+          <t>Q163</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Q158</t>
+          <t>Q172</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Q161</t>
+          <t>MTQ-024</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Q163</t>
+          <t>MTQ-048</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Q172</t>
+          <t>MTQ-020</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MTQ-024</t>
+          <t>Q242</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MTQ-048</t>
+          <t>Q252</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MTQ-020</t>
+          <t>Q173</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Q242</t>
+          <t>Q286</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Q252</t>
+          <t>MTQ-053</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Q173</t>
+          <t>Q244</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Q286</t>
+          <t>MTQ-073</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MTQ-053</t>
+          <t>MTQ-032</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Q244</t>
+          <t>MTQ-075</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MTQ-073</t>
+          <t>Q107</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MTQ-032</t>
+          <t>Q108</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MTQ-075</t>
+          <t>Q245</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Q107</t>
+          <t>Q112</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Q108</t>
+          <t>Q164</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Q245</t>
+          <t>Q254</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Q112</t>
+          <t>Q261</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Q109</t>
+          <t>Q098</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Q098</t>
+          <t>Q114</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Q114</t>
+          <t>MTQ-078</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MTQ-078</t>
+          <t>MTQ-055</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MTQ-055</t>
+          <t>MTQ-056</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MTQ-056</t>
+          <t>Q110</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Q110</t>
+          <t>Q102</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Q102</t>
+          <t>Q121</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Q121</t>
+          <t>MTQ-076</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MTQ-076</t>
+          <t>MTQ-009</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MTQ-009</t>
+          <t>MTQ-061</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MTQ-061</t>
+          <t>MTQ-028</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MTQ-028</t>
+          <t>MTQ-072</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MTQ-072</t>
+          <t>Q142</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Q142</t>
+          <t>Q222</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Q222</t>
+          <t>Q179</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Q179</t>
+          <t>Q168</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Q168</t>
+          <t>MTQ-027</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Q157</t>
+          <t>MTQ-060</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MTQ-027</t>
+          <t>MTQ-025</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MTQ-060</t>
+          <t>MTQ-003</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MTQ-025</t>
+          <t>Q298</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MTQ-003</t>
+          <t>MTQ-005</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Q298</t>
+          <t>Q066</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MTQ-005</t>
+          <t>Q248</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Q066</t>
+          <t>Q255</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Q248</t>
+          <t>Q199</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Q255</t>
+          <t>MTQ-059</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Q199</t>
+          <t>MTQ-029</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MTQ-059</t>
+          <t>MTQ-047</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MTQ-029</t>
+          <t>Q115</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MTQ-047</t>
+          <t>Q247</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Q115</t>
+          <t>Q263</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Q247</t>
+          <t>Q264</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q076</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Q076</t>
+          <t>MTQ-005</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MTQ-005</t>
+          <t>Q026</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q037</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>MTQ-034</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MTQ-034</t>
+          <t>MTQ-067</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MTQ-067</t>
+          <t>MTQ-017</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MTQ-017</t>
+          <t>Q135</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Q135</t>
+          <t>MTQ-054</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MTQ-054</t>
+          <t>Q122</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Q122</t>
+          <t>Q111</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Q111</t>
+          <t>Q104</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Q104</t>
+          <t>Q100</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Q100</t>
+          <t>Q142</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Q142</t>
+          <t>Q148</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Q096</t>
+          <t>Q060</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Q148</t>
+          <t>Q099</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Q060</t>
+          <t>MTQ-062</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Q099</t>
+          <t>MTQ-036</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>MTQ-062</t>
+          <t>MTQ-040</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>MTQ-036</t>
+          <t>MTQ-064</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>MTQ-040</t>
+          <t>Q150</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MTQ-064</t>
+          <t>MTQ-057</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Q150</t>
+          <t>Q175</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MTQ-057</t>
+          <t>Q182</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Q175</t>
+          <t>Q189</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Q182</t>
+          <t>MTQ-008</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Q189</t>
+          <t>MTQ-018</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>MTQ-008</t>
+          <t>MTQ-037</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>MTQ-018</t>
+          <t>Q246</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MTQ-037</t>
+          <t>Q244</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Q246</t>
+          <t>Q258</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Q244</t>
+          <t>Q205</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Q258</t>
+          <t>Q256</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Q205</t>
+          <t>Q259</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Q256</t>
+          <t>MTQ-026</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Q259</t>
+          <t>MTQ-044</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>MTQ-026</t>
+          <t>MTQ-071</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MTQ-044</t>
+          <t>Q117</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>MTQ-071</t>
+          <t>Q155</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Q117</t>
+          <t>Q029</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Q155</t>
+          <t>Q166</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q265</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Q096</t>
+          <t>MTQ-030</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>MTQ-030</t>
+          <t>Q133</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Q133</t>
+          <t>Q104</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Q104</t>
+          <t>Q141</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Q141</t>
+          <t>Q101</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Q092</t>
+          <t>MTQ-046</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Q093</t>
+          <t>MTQ-014</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Q101</t>
+          <t>MTQ-039</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>MTQ-046</t>
+          <t>Q151</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>MTQ-014</t>
+          <t>Q169</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>MTQ-039</t>
+          <t>Q165</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Q151</t>
+          <t>MTQ-079</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Q169</t>
+          <t>Q210</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Q165</t>
+          <t>Q223</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>MTQ-079</t>
+          <t>MTQ-019</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Q210</t>
+          <t>MTQ-023</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Q223</t>
+          <t>MTQ-011</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>MTQ-019</t>
+          <t>Q253</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>MTQ-023</t>
+          <t>MTQ-080</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>MTQ-011</t>
+          <t>Q260</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Q253</t>
+          <t>Q286</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>MTQ-080</t>
+          <t>Q257</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Q260</t>
+          <t>Q274</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Q286</t>
+          <t>Q262</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Q257</t>
+          <t>MTQ-042</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Q274</t>
+          <t>MTQ-043</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Q262</t>
+          <t>MTQ-074</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>MTQ-042</t>
+          <t>Q162</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>MTQ-043</t>
+          <t>Q031</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>MTQ-074</t>
+          <t>Q033</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Q162</t>
+          <t>Q266</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4466,6 +4466,11 @@
           <t>explanation_en</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>category_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4523,6 +4528,11 @@
           <t>A passenger aged 15 or over is personally responsible for wearing their own seat belt, so the 17-year-old Elviira is responsible for buckling up herself.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4580,6 +4590,11 @@
           <t>The driver is always legally responsible for adapting speed to prevailing conditions; a passenger's request cannot override the duty to drive safely.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4637,6 +4652,11 @@
           <t>A Finnish taxi driver's licence is granted without a geographic restriction and is valid across all of mainland Finland, so Aulis can work for any employer anywhere in the country without any additional test or application.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4694,6 +4714,11 @@
           <t>In heavy traffic near a pedestrian crossing, driver attention must stay on the road; interacting with devices must wait until conditions allow it safely.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4751,6 +4776,11 @@
           <t>Finnish law requires the alcohol interlock fitted to school and day-care transport vehicles to prevent engine start at a threshold of 0.10 mg/l of exhaled breath, ensuring a strict near-zero tolerance for these vulnerable-passenger services.</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4808,6 +4838,11 @@
           <t>The driver is responsible for ensuring that luggage is secured so it cannot become a dangerous projectile during sudden braking, regardless of the passenger's preference.</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4865,6 +4900,11 @@
           <t>Stopping in a dangerous position on a narrow street with poor visibility and following traffic puts both the passenger and other road users at risk, so the driver must proceed to a safe stopping point.</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4922,6 +4962,11 @@
           <t>Transparent, calm communication about an unavoidable route change builds trust and resolves the passenger's concern without conflict, which is the core of good customer service.</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4979,6 +5024,11 @@
           <t>The passenger has disclosed a medical condition and made a specific, reasonable request; honouring it by giving advance notice of the route change is both good customer service and a duty of care.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5036,6 +5086,11 @@
           <t>A passenger has the right to understand how their fare is calculated; giving an honest, professional explanation maintains trust and meets the transparency requirements of good taxi service.</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5093,6 +5148,11 @@
           <t>Maintaining a calm, professional demeanour de-escalates the situation, while continuously monitoring safety allows the driver to decide whether further action — such as ending the journey — is warranted.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5150,6 +5210,11 @@
           <t>Stopping on a pedestrian crossing is illegal and dangerous; the driver should find the nearest lawful stopping point and then assist the mobility-impaired passenger appropriately.</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5207,6 +5272,11 @@
           <t>A powered wheelchair must be properly secured before the vehicle moves; checking and confirming safe fastening in advance is a legal and safety obligation regardless of journey length.</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5264,6 +5334,11 @@
           <t>Finnish law requires taxi drivers to carry guide dogs at no extra charge and to allow them to remain with their owner, as guide dogs are an essential mobility aid for visually impaired passengers.</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5321,6 +5396,11 @@
           <t>A confused passenger trying to open a moving car door is an immediate safety hazard; the driver must bring the vehicle to a safe stop promptly to prevent injury.</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5378,6 +5458,11 @@
           <t>A passenger's injury creates a duty to assist, but safety rules still apply; the driver must find the nearest safe and lawful stop and then help the passenger as much as practicable.</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5435,6 +5520,11 @@
           <t>The driver has an ongoing duty of care until the passenger has safely exited the vehicle; alerting them to cycle traffic on the right prevents a potentially serious 'dooring' collision.</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5492,6 +5582,11 @@
           <t>A taxi driver has a legal and professional obligation to handle found property according to company or dispatch-centre procedures and to act promptly to return it to its owner.</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5549,6 +5644,11 @@
           <t>Transparently informing the passenger about any fare or terms change before proceeding protects both parties and meets the legal requirement for clear pricing in taxi services.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5606,6 +5706,11 @@
           <t>Verifying both the passenger's identity and the booking before departing prevents taking the wrong person, protects the genuine customer, and ensures correct billing.</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5663,6 +5768,11 @@
           <t>Staying calm and explaining the reasoning professionally de-escalates tension while still serving the passenger's best interests and maintaining safety.</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5720,6 +5830,11 @@
           <t>The driver is responsible for ensuring passengers can exit the vehicle safely, which means finding an alternative stopping point when the requested location poses a danger to the passenger or other road users.</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5777,6 +5892,11 @@
           <t>Providing a clear and complete receipt on request is a basic legal and customer-service obligation for taxi drivers, regardless of the payment method used.</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5834,6 +5954,11 @@
           <t>A driver may accommodate a passenger's route preference when the alternative route is legal and safe, as good customer service includes respecting reasonable passenger wishes.</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5891,6 +6016,11 @@
           <t>Good customer service means respecting the passenger's personal preferences, including their wish for a quiet journey, while still fulfilling all safety duties.</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5948,6 +6078,11 @@
           <t>The driver has a duty of care to ensure that passengers can alight safely, which overrides an unsafe stopping request from the passenger.</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6005,6 +6140,11 @@
           <t>Handling a payment dispute calmly and professionally, following the service's procedures, protects both the driver's interests and the passenger's dignity without making unfounded accusations.</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6062,6 +6202,11 @@
           <t>Adapting your driving style to a passenger's health needs is part of the duty of care, and staying calm and in control ensures both passenger comfort and road safety.</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6119,6 +6264,11 @@
           <t>Any uncertainty about brake function poses a direct safety risk to passengers and other road users, so the vehicle must be checked before carrying further passengers.</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6176,6 +6326,11 @@
           <t>A passenger with no sight cannot locate the vehicle or navigate to it independently, so the driver must go to the passenger, announce their arrival, introduce themselves, and guide the passenger to ensure a safe and dignified boarding experience.</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6233,6 +6388,11 @@
           <t>Driving with a known tyre fault endangers passengers and other road users, so the vehicle must be roadworthy before any journey begins.</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6290,6 +6450,11 @@
           <t>The driver has a duty to ensure passengers wear seat belts; a calm reminder is the appropriate first step and does not itself create a new safety hazard.</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6347,6 +6512,11 @@
           <t>Elderly and mobility-impaired passengers are entitled to assistance; the driver must allow sufficient time and provide hands-on help to ensure a safe and dignified journey.</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6404,6 +6574,11 @@
           <t>On a slippery surface the risk of a fall is high, so the driver must get out and actively assist the passenger to board safely and stow their mobility aid before setting off.</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6461,6 +6636,11 @@
           <t>When a passenger reports poor balance, the driver must take extra care to verify that they are safely seated, their mobility aid is secured, and they are belted before any movement begins.</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6518,6 +6698,11 @@
           <t>Clarifying the destination before departure prevents taking the passenger to the wrong place and ensures both parties have a clear, agreed understanding of the journey.</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6575,6 +6760,11 @@
           <t>Loose luggage in the passenger compartment is a serious safety hazard in any collision or sudden stop, so the driver must refuse unsafe loading regardless of passenger consent or journey length.</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6632,6 +6822,11 @@
           <t>A child standing in a moving vehicle is a direct safety risk; the driver must intervene calmly and, if needed, stop safely to restore order before continuing.</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6689,6 +6884,11 @@
           <t>A child who requires a restraint system must not be transported without one; the driver's duty to protect the child's safety overrides any pressure to complete the trip.</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6746,6 +6946,11 @@
           <t>When a passenger has a hearing impairment, the driver must adapt their communication method — using eye contact, clear speech, or written confirmation — to ensure the destination and other key information are correctly understood.</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6803,6 +7008,11 @@
           <t>A hearing-impaired passenger needs clear, non-verbal confirmation of the destination; calmly verifying via written or visual means ensures they feel understood and travel to the correct place safely.</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6860,6 +7070,11 @@
           <t>A BUS lane marking restricts the lane to buses and any other vehicles explicitly authorised by accompanying traffic signs; taxis may only use it if a sign permits them.</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6917,6 +7132,11 @@
           <t>The uneven road / bump warning sign alerts drivers to rough or bumpy road conditions ahead so they can reduce speed and protect passengers from jolts.</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6974,6 +7194,11 @@
           <t>Stopping on the carriageway close to the kerb (without mounting the pavement) is the correct and lawful way to set down or pick up passengers while keeping the pavement clear for pedestrians.</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7031,6 +7256,11 @@
           <t>The driver is legally responsible for ensuring all passengers wear seat belts; journey length is irrelevant, and a child cannot waive this legal safety requirement.</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7088,6 +7318,11 @@
           <t>A child showing signs of sensory overload needs a calm, low-stimulus environment; the driver must reduce unnecessary input and allow the child time to respond, ensuring a safe and comfortable journey.</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7145,6 +7380,11 @@
           <t>Looking away from the road — even briefly or at low speed — is dangerous near vulnerable road users; the driver must not be distracted and should only check new information when safely stopped.</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7202,6 +7442,11 @@
           <t>Passengers have the right to a receipt and a transparent breakdown of the fare; providing this is both a legal obligation and good customer service in the taxi profession.</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7259,6 +7504,11 @@
           <t>Passenger safety takes priority; when a passenger reports feeling unwell the driver must stop safely as soon as possible and assess whether emergency assistance is needed.</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7316,6 +7566,11 @@
           <t>The driver has a duty of care for property left in the vehicle; checking promptly and following lost-property procedures ensures the passenger's belongings are handled correctly and returned.</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7373,6 +7628,11 @@
           <t>Under Finnish law a taxi driver is responsible for ensuring all passengers wear seat belts, regardless of the passenger's age or whether the journey is a school transport service.</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7430,6 +7690,11 @@
           <t>A wheelchair must be properly fastened to prevent movement in every direction, not only sideways, to keep the passenger safe in the event of sudden braking or a collision.</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7487,6 +7752,11 @@
           <t>A 'motor vehicles prohibited' sign includes an exception for access to properties on that street, so a taxi may enter the street when its destination is a property along it.</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7544,6 +7814,11 @@
           <t>Introducing yourself, stating your location, and offering physical guidance respects the visually impaired passenger's autonomy and dignity while ensuring they can board safely.</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7601,6 +7876,11 @@
           <t>Stopping safely and proactively approaching a slow-moving passenger to offer assistance ensures their physical safety and dignity during boarding.</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7658,6 +7938,11 @@
           <t>Confirming the destination and fare in writing or via a map ensures a deaf passenger fully understands the journey details before departure, preventing misunderstandings.</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7715,6 +8000,11 @@
           <t>Using a phone without a hands-free device while driving is illegal and dangerous; the driver must not answer and should call back after the journey.</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7772,6 +8062,11 @@
           <t>A passenger with a memory disorder must be handled with patience; using the contact information they are carrying to verify the correct destination ensures their safety and wellbeing.</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7829,6 +8124,11 @@
           <t>Passenger and traffic safety must take precedence over journey time; a slightly longer but safer route is always the correct professional choice for a taxi driver.</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7886,6 +8186,11 @@
           <t>Agreeing on a lawful stopping point that is safe and accessible for the passenger is the professional approach, respecting both traffic rules and the passenger's needs.</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7943,6 +8248,11 @@
           <t>A visually impaired passenger cannot see gestures or visual cues, so clear verbal instructions are the only way to guide them safely to the entrance.</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8000,6 +8310,11 @@
           <t>Finnish law requires taxi drivers to accept guide dogs, and good customer service means actively assisting the visually impaired passenger with verbal guidance and safe boarding.</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8057,6 +8372,11 @@
           <t>Drivers are legally obliged to transport guide dogs and must not refuse service; the dog's placement in the foot well is the passenger's decision and poses no problem.</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8114,6 +8434,11 @@
           <t>Applying the Sunday tariff rates from the price list to a 20 km, 30-minute single-passenger journey yields a total of 65.00 €.</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8171,6 +8496,11 @@
           <t>Road traffic law requires that children travel with appropriate restraints; a guardian's lap provides no protection in a collision, and the driver bears responsibility for passenger safety.</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8228,6 +8558,11 @@
           <t>Respecting the customer's own instructions ensures both safety and dignity; they know their body best, and calm, guided assistance prevents injury.</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8285,6 +8620,11 @@
           <t>A mispositioned seat belt on a wheelchair passenger is a safety hazard; it must be corrected before the vehicle moves, regardless of time pressure.</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8342,6 +8682,11 @@
           <t>Mobility scooters are not approved as passenger seats in vehicles; only purpose-built wheelchair restraint systems meet the required safety standards for transporting seated passengers.</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8399,6 +8744,11 @@
           <t>Asking how you can help and providing verbal orientation are the basic duties of good customer service for a visually impaired passenger; drivers may not refuse or impose conditions.</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8456,6 +8806,11 @@
           <t>The guide dog travels in the foot well or luggage space — it is a working animal and should not be interfered with, and drivers must accept it in these designated spaces.</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8513,6 +8868,11 @@
           <t>An unsecured suitcase becomes a dangerous projectile in an emergency stop; the driver is responsible for safe loading regardless of the passenger's time pressure.</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8570,6 +8930,11 @@
           <t>Taxi drivers are required by professional standards to treat all customers politely and respectfully at all times, regardless of personal mood, and customers are entitled to complain about rude treatment.</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8627,6 +8992,11 @@
           <t>A driver is solely responsible for the safety of any manoeuvre; a passenger's request does not override the driver's legal duty to overtake only when it is safe to do so.</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8684,6 +9054,11 @@
           <t>Finnish road traffic law requires a clear field of vision before driving; an iced windscreen is a legal violation and a direct safety hazard that must be cleared before moving.</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8741,6 +9116,11 @@
           <t>Driving while fatigued is as dangerous as drink-driving; a professional driver is legally and ethically obliged to refuse to drive when they cannot do so safely.</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>traffic_safety</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8798,6 +9178,11 @@
           <t>Good customer service for visually impaired passengers means asking how you can help and providing verbal information about the environment, since they cannot observe it themselves.</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8855,6 +9240,11 @@
           <t>Opening a door into cycle traffic can cause serious injury to cyclists; the driver must ensure the passenger exits safely even when there is a language barrier, using clear gestures and confirming understanding.</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>passenger_safety</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8912,6 +9302,11 @@
           <t>Transporting children and wheelchair users in rehabilitation trips requires specific training and approval; operating without the required qualifications would violate the conditions of the contract and endanger the passenger.</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>special_needs</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8969,6 +9364,11 @@
           <t>A taxi driver is legally obliged to return found property immediately; taking it home or delaying could constitute misappropriation of lost property.</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>customer_service</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9024,6 +9424,11 @@
       <c r="K81" t="inlineStr">
         <is>
           <t>Standard first aid for an epileptic seizure is to protect the head and place the person in the recovery position once convulsions ease; restraining the person or ignoring the seizure are both harmful and negligent.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>special_needs</t>
         </is>
       </c>
     </row>

--- a/content/sources/model_test_workbook.xlsx
+++ b/content/sources/model_test_workbook.xlsx
@@ -2099,7 +2099,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Q164</t>
+          <t>Q167</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Q166</t>
+          <t>Q170</t>
         </is>
       </c>
     </row>
